--- a/new original/_Dialog/Drama/kettle.xlsx
+++ b/new original/_Dialog/Drama/kettle.xlsx
@@ -299,12 +299,12 @@
 I did not share her past to speak of tragedies or the villagers' folly.</t>
   </si>
   <si>
-    <t xml:space="preserve">あの日…村を訪れた私が見たのは、命あるもの全てが死に絶えた凄惨な光景だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
+    <t xml:space="preserve">あの日…村を訪れた私を待っていたは、命あるもの全てが死に絶えた凄惨な静寂だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
 あの子は特別な力の元に生まれ、その力は確実に、彼女を取り巻くものたちの運命に影響を与えるだろう。
 もし君たちが望むなら、私とクルイツゥアは出ていくから、いつでも言ってくれ。</t>
   </si>
   <si>
-    <t xml:space="preserve">That day... what I saw when I visited the village was a horrific scene of death where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
+    <t xml:space="preserve">That day... what awaited me in the village I visited was a horrific silence of death　where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
 She was born under a peculiar power, and that power will undoubtedly affect the fates of those around her.
 If you ever wish us to leave, just say so.</t>
   </si>
@@ -1836,7 +1836,7 @@
     <t xml:space="preserve">お、おほん…ということだ、#pcよ。
 この決断は私には荷が重い。お前に任せよう。
 死者の洞窟に赴き、「淀み」を見つけるんだ。そこでイスシズルに渡されたこの瓶を使うか、あるいはファリスさんに渡された「聖水」を使うか…それはお前次第だ、よく考えてくれ。
-…安心しろ、私もついていってやる。お前だけに責任を追わせるのは酷だからな。</t>
+…安心しろ、私もついていってやる。お前だけに責任を負わせるのは酷だからな。</t>
   </si>
   <si>
     <t xml:space="preserve">A-hem... So then, #pc.

--- a/new original/_Dialog/Drama/kettle.xlsx
+++ b/new original/_Dialog/Drama/kettle.xlsx
@@ -299,12 +299,12 @@
 I did not share her past to speak of tragedies or the villagers' folly.</t>
   </si>
   <si>
-    <t xml:space="preserve">あの日…村を訪れた私を待っていたは、命あるもの全てが死に絶えた凄惨な静寂だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
+    <t xml:space="preserve">あの日…村を訪れた私が見たのは、命あるもの全てが死に絶えた凄惨な光景だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
 あの子は特別な力の元に生まれ、その力は確実に、彼女を取り巻くものたちの運命に影響を与えるだろう。
 もし君たちが望むなら、私とクルイツゥアは出ていくから、いつでも言ってくれ。</t>
   </si>
   <si>
-    <t xml:space="preserve">That day... what awaited me in the village I visited was a horrific silence of death　where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
+    <t xml:space="preserve">That day... what I saw when I visited the village was a horrific scene of death where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
 She was born under a peculiar power, and that power will undoubtedly affect the fates of those around her.
 If you ever wish us to leave, just say so.</t>
   </si>
@@ -1836,7 +1836,7 @@
     <t xml:space="preserve">お、おほん…ということだ、#pcよ。
 この決断は私には荷が重い。お前に任せよう。
 死者の洞窟に赴き、「淀み」を見つけるんだ。そこでイスシズルに渡されたこの瓶を使うか、あるいはファリスさんに渡された「聖水」を使うか…それはお前次第だ、よく考えてくれ。
-…安心しろ、私もついていってやる。お前だけに責任を負わせるのは酷だからな。</t>
+…安心しろ、私もついていってやる。お前だけに責任を追わせるのは酷だからな。</t>
   </si>
   <si>
     <t xml:space="preserve">A-hem... So then, #pc.
